--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129096573</v>
       </c>
       <c r="B3" t="n">
-        <v>89530</v>
+        <v>89533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92083</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100745</v>
+        <v>100750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129096598</v>
       </c>
       <c r="B8" t="n">
-        <v>88729</v>
+        <v>88732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129096573</v>
       </c>
       <c r="B3" t="n">
-        <v>89533</v>
+        <v>89536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100750</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129096598</v>
       </c>
       <c r="B8" t="n">
-        <v>88732</v>
+        <v>88735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,6 +1407,215 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129254784</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96013</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>521355</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6553383</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson, Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129254787</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>521397</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553357</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson, Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129096573</v>
       </c>
       <c r="B3" t="n">
-        <v>89536</v>
+        <v>89540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92091</v>
+        <v>92098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129096598</v>
       </c>
       <c r="B8" t="n">
-        <v>88735</v>
+        <v>88739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96013</v>
+        <v>96015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106292</v>
+        <v>106294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,6 +1615,414 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129259996</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100857</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>521332</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6553404</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129260021</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106294</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>521411</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6553315</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129260022</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106294</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>521374</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6553324</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129260020</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106294</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521332</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6553404</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129096573</v>
       </c>
       <c r="B3" t="n">
-        <v>89540</v>
+        <v>89547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92098</v>
+        <v>92105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100763</v>
+        <v>100770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129096598</v>
       </c>
       <c r="B8" t="n">
-        <v>88739</v>
+        <v>88746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96015</v>
+        <v>96022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129096573</v>
       </c>
       <c r="B3" t="n">
-        <v>89547</v>
+        <v>89549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92105</v>
+        <v>92107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100770</v>
+        <v>100772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129096598</v>
       </c>
       <c r="B8" t="n">
-        <v>88746</v>
+        <v>88748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96022</v>
+        <v>96024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129096573</v>
       </c>
       <c r="B3" t="n">
-        <v>89549</v>
+        <v>89550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92107</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100772</v>
+        <v>100798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129096598</v>
       </c>
       <c r="B8" t="n">
-        <v>88748</v>
+        <v>88749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96024</v>
+        <v>96050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100798</v>
+        <v>100799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96050</v>
+        <v>96051</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100799</v>
+        <v>100800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96051</v>
+        <v>96052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson, Hans Rydberg</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson, Hans Rydberg</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096607</v>
       </c>
       <c r="B2" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129096573</v>
       </c>
       <c r="B3" t="n">
-        <v>89550</v>
+        <v>89553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129096601</v>
       </c>
       <c r="B4" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129096594</v>
       </c>
       <c r="B5" t="n">
-        <v>100800</v>
+        <v>100804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>129096578</v>
       </c>
       <c r="B6" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129096599</v>
       </c>
       <c r="B7" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129096598</v>
       </c>
       <c r="B8" t="n">
-        <v>88749</v>
+        <v>88752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96052</v>
+        <v>96056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1412,7 +1412,7 @@
         <v>129254784</v>
       </c>
       <c r="B9" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129254787</v>
       </c>
       <c r="B10" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -1621,7 +1621,7 @@
         <v>129259996</v>
       </c>
       <c r="B11" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129260021</v>
       </c>
       <c r="B12" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>129260022</v>
       </c>
       <c r="B13" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129260020</v>
       </c>
       <c r="B14" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2024,6 +2024,783 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133622988</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107624</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>521357</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6553478</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133622991</v>
+      </c>
+      <c r="B16" t="n">
+        <v>107624</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521383</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6553441</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133622990</v>
+      </c>
+      <c r="B17" t="n">
+        <v>107624</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6553446</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133622996</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106170</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>521367</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6553307</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133622986</v>
+      </c>
+      <c r="B19" t="n">
+        <v>107624</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>521370</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6553485</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133622992</v>
+      </c>
+      <c r="B20" t="n">
+        <v>107624</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>521391</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6553439</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133622989</v>
+      </c>
+      <c r="B21" t="n">
+        <v>107624</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521397</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6553453</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B17" t="n">
-        <v>107624</v>
+        <v>106170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R17" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B18" t="n">
-        <v>106170</v>
+        <v>107624</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R18" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B17" t="n">
-        <v>106170</v>
+        <v>107624</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R17" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B18" t="n">
-        <v>107624</v>
+        <v>106170</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R18" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>133622988</v>
       </c>
       <c r="B15" t="n">
-        <v>107624</v>
+        <v>107626</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107624</v>
+        <v>107626</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B17" t="n">
-        <v>106170</v>
+        <v>107626</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R17" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B18" t="n">
-        <v>107624</v>
+        <v>106172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R18" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2473,7 +2473,7 @@
         <v>133622986</v>
       </c>
       <c r="B19" t="n">
-        <v>107624</v>
+        <v>107626</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>133622992</v>
       </c>
       <c r="B20" t="n">
-        <v>107624</v>
+        <v>107626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>133622989</v>
       </c>
       <c r="B21" t="n">
-        <v>107624</v>
+        <v>107626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>133622988</v>
       </c>
       <c r="B15" t="n">
-        <v>107626</v>
+        <v>107634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107626</v>
+        <v>107634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>133622990</v>
       </c>
       <c r="B17" t="n">
-        <v>107626</v>
+        <v>107634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>133622996</v>
       </c>
       <c r="B18" t="n">
-        <v>106172</v>
+        <v>106180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>133622986</v>
       </c>
       <c r="B19" t="n">
-        <v>107626</v>
+        <v>107634</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>133622992</v>
       </c>
       <c r="B20" t="n">
-        <v>107626</v>
+        <v>107634</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>133622989</v>
       </c>
       <c r="B21" t="n">
-        <v>107626</v>
+        <v>107634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>133622988</v>
       </c>
       <c r="B15" t="n">
-        <v>107634</v>
+        <v>107662</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107634</v>
+        <v>107662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B17" t="n">
-        <v>107634</v>
+        <v>106208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R17" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B18" t="n">
-        <v>106180</v>
+        <v>107662</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R18" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2473,7 +2473,7 @@
         <v>133622986</v>
       </c>
       <c r="B19" t="n">
-        <v>107634</v>
+        <v>107662</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>133622992</v>
       </c>
       <c r="B20" t="n">
-        <v>107634</v>
+        <v>107662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>133622989</v>
       </c>
       <c r="B21" t="n">
-        <v>107634</v>
+        <v>107662</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B17" t="n">
-        <v>106208</v>
+        <v>107662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R17" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B18" t="n">
-        <v>107662</v>
+        <v>106208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R18" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>133622988</v>
       </c>
       <c r="B15" t="n">
-        <v>107662</v>
+        <v>107672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107662</v>
+        <v>107672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B17" t="n">
-        <v>107662</v>
+        <v>106218</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R17" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B18" t="n">
-        <v>106208</v>
+        <v>107672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R18" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2473,7 +2473,7 @@
         <v>133622986</v>
       </c>
       <c r="B19" t="n">
-        <v>107662</v>
+        <v>107672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>133622992</v>
       </c>
       <c r="B20" t="n">
-        <v>107662</v>
+        <v>107672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>133622989</v>
       </c>
       <c r="B21" t="n">
-        <v>107662</v>
+        <v>107672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B17" t="n">
-        <v>106218</v>
+        <v>107672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R17" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B18" t="n">
-        <v>107672</v>
+        <v>106218</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R18" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>133622988</v>
       </c>
       <c r="B15" t="n">
-        <v>107672</v>
+        <v>107673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107672</v>
+        <v>107673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>133622990</v>
       </c>
       <c r="B17" t="n">
-        <v>107672</v>
+        <v>107673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>133622996</v>
       </c>
       <c r="B18" t="n">
-        <v>106218</v>
+        <v>106219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>133622986</v>
       </c>
       <c r="B19" t="n">
-        <v>107672</v>
+        <v>107673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>133622992</v>
       </c>
       <c r="B20" t="n">
-        <v>107672</v>
+        <v>107673</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>133622989</v>
       </c>
       <c r="B21" t="n">
-        <v>107672</v>
+        <v>107673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>133622988</v>
       </c>
       <c r="B15" t="n">
-        <v>107673</v>
+        <v>107675</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107673</v>
+        <v>107675</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>133622990</v>
       </c>
       <c r="B17" t="n">
-        <v>107673</v>
+        <v>107675</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>133622996</v>
       </c>
       <c r="B18" t="n">
-        <v>106219</v>
+        <v>106221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>133622986</v>
       </c>
       <c r="B19" t="n">
-        <v>107673</v>
+        <v>107675</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>133622992</v>
       </c>
       <c r="B20" t="n">
-        <v>107673</v>
+        <v>107675</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>133622989</v>
       </c>
       <c r="B21" t="n">
-        <v>107673</v>
+        <v>107675</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622990</v>
+        <v>133622996</v>
       </c>
       <c r="B17" t="n">
-        <v>107676</v>
+        <v>106222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521393</v>
+        <v>521367</v>
       </c>
       <c r="R17" t="n">
-        <v>6553446</v>
+        <v>6553307</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622996</v>
+        <v>133622990</v>
       </c>
       <c r="B18" t="n">
-        <v>106222</v>
+        <v>107676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521367</v>
+        <v>521393</v>
       </c>
       <c r="R18" t="n">
-        <v>6553307</v>
+        <v>6553446</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -2029,7 +2029,7 @@
         <v>133622988</v>
       </c>
       <c r="B15" t="n">
-        <v>107676</v>
+        <v>107683</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107676</v>
+        <v>107683</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>133622996</v>
       </c>
       <c r="B17" t="n">
-        <v>106222</v>
+        <v>106229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>133622990</v>
       </c>
       <c r="B18" t="n">
-        <v>107676</v>
+        <v>107683</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>133622986</v>
       </c>
       <c r="B19" t="n">
-        <v>107676</v>
+        <v>107683</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>133622992</v>
       </c>
       <c r="B20" t="n">
-        <v>107676</v>
+        <v>107683</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>133622989</v>
       </c>
       <c r="B21" t="n">
-        <v>107676</v>
+        <v>107683</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129096607</v>
+        <v>129096616</v>
       </c>
       <c r="B2" t="n">
-        <v>100916</v>
+        <v>92244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>721</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Grifola frondosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Dicks.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521476</v>
+        <v>521470</v>
       </c>
       <c r="R2" t="n">
-        <v>6553172</v>
+        <v>6553226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +769,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>på ek</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,45 +791,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129096573</v>
+        <v>129096598</v>
       </c>
       <c r="B3" t="n">
-        <v>89562</v>
+        <v>89104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5581</v>
+        <v>805</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521431</v>
+        <v>521471</v>
       </c>
       <c r="R3" t="n">
-        <v>6553183</v>
+        <v>6553126</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,18 +879,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Lövskog på kalkrik mark</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>lövved</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -885,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129096601</v>
+        <v>122955281</v>
       </c>
       <c r="B4" t="n">
-        <v>92136</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,37 +913,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testaskogen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521492</v>
+        <v>521412</v>
       </c>
       <c r="R4" t="n">
-        <v>6553127</v>
+        <v>6553514</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -950,12 +978,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>död jättealm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,36 +1009,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövskog på kalkrik mark</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>på nedfallen hasselgren</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129096594</v>
+        <v>129254784</v>
       </c>
       <c r="B5" t="n">
-        <v>100821</v>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521437</v>
+        <v>521355</v>
       </c>
       <c r="R5" t="n">
-        <v>6553126</v>
+        <v>6553383</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,12 +1090,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,27 +1110,32 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129096578</v>
+        <v>1173387</v>
       </c>
       <c r="B6" t="n">
-        <v>100916</v>
+        <v>92497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,37 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521465</v>
+        <v>521324</v>
       </c>
       <c r="R6" t="n">
-        <v>6553182</v>
+        <v>6553489</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2011-11-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2011-11-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,28 +1216,33 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Lövskog på kalkrik mark</t>
+          <t>ek/hasselskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129096599</v>
+        <v>1173388</v>
       </c>
       <c r="B7" t="n">
-        <v>100916</v>
+        <v>92497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,37 +1250,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521497</v>
+        <v>521319</v>
       </c>
       <c r="R7" t="n">
-        <v>6553139</v>
+        <v>6553486</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2011-11-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2011-11-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,72 +1323,68 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Lövskog på kalkrik mark</t>
+          <t>ek/hasselskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Andersson, Björn Gunnarsson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129096598</v>
+        <v>129096601</v>
       </c>
       <c r="B8" t="n">
-        <v>88759</v>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>805</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521471</v>
+        <v>521492</v>
       </c>
       <c r="R8" t="n">
-        <v>6553126</v>
+        <v>6553127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1431,11 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>på nedfallen hasselgren</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1409,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254784</v>
+        <v>129259884</v>
       </c>
       <c r="B9" t="n">
-        <v>96114</v>
+        <v>81655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,37 +1464,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>3929</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, skog SO om, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521355</v>
+        <v>521338</v>
       </c>
       <c r="R9" t="n">
-        <v>6553383</v>
+        <v>6553500</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,18 +1537,23 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Lövskog på kalkrik mark</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Hans Rydberg</t>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1516,48 +1565,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254787</v>
+        <v>129096617</v>
       </c>
       <c r="B10" t="n">
-        <v>106396</v>
+        <v>91867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>5445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521397</v>
+        <v>521470</v>
       </c>
       <c r="R10" t="n">
-        <v>6553357</v>
+        <v>6553226</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1639,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,27 +1659,32 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>på ek</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Michael Andersson, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129259996</v>
+        <v>129096573</v>
       </c>
       <c r="B11" t="n">
-        <v>100958</v>
+        <v>89902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,37 +1692,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>5581</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Britzelm.) Sacc.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521332</v>
+        <v>521431</v>
       </c>
       <c r="R11" t="n">
-        <v>6553404</v>
+        <v>6553183</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,12 +1746,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1697,50 +1760,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>lövved</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Michael Andersson, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129260021</v>
+        <v>133622986</v>
       </c>
       <c r="B12" t="n">
-        <v>106397</v>
+        <v>107690</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>219686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1748,20 +1817,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521411</v>
+        <v>521370</v>
       </c>
       <c r="R12" t="n">
-        <v>6553315</v>
+        <v>6553485</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,12 +1863,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,45 +1882,45 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Ädellövskog, tidigare ekhage</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129260022</v>
+        <v>133622988</v>
       </c>
       <c r="B13" t="n">
-        <v>106397</v>
+        <v>107690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>219686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1850,20 +1928,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521374</v>
+        <v>521357</v>
       </c>
       <c r="R13" t="n">
-        <v>6553324</v>
+        <v>6553478</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,12 +1974,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,45 +1993,45 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Ädellövskog, tidigare ekhage</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129260020</v>
+        <v>133622989</v>
       </c>
       <c r="B14" t="n">
-        <v>106397</v>
+        <v>107690</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>219686</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1952,20 +2039,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Testa, skog SO om, Nrk</t>
+          <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521332</v>
+        <v>521397</v>
       </c>
       <c r="R14" t="n">
-        <v>6553404</v>
+        <v>6553453</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,12 +2085,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2008,28 +2104,28 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Ädellövskog, tidigare ekhage</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Björn Gunnarsson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133622988</v>
+        <v>133622990</v>
       </c>
       <c r="B15" t="n">
-        <v>107683</v>
+        <v>107690</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2152,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2070,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521357</v>
+        <v>521393</v>
       </c>
       <c r="R15" t="n">
-        <v>6553478</v>
+        <v>6553446</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2140,7 +2236,7 @@
         <v>133622991</v>
       </c>
       <c r="B16" t="n">
-        <v>107683</v>
+        <v>107690</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133622996</v>
+        <v>133622992</v>
       </c>
       <c r="B17" t="n">
-        <v>106229</v>
+        <v>107690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2355,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2278,7 +2374,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2292,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521367</v>
+        <v>521391</v>
       </c>
       <c r="R17" t="n">
-        <v>6553307</v>
+        <v>6553439</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2359,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133622990</v>
+        <v>133623000</v>
       </c>
       <c r="B18" t="n">
-        <v>107683</v>
+        <v>107690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2389,7 +2485,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2403,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521393</v>
+        <v>521425</v>
       </c>
       <c r="R18" t="n">
-        <v>6553446</v>
+        <v>6553358</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2470,27 +2566,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133622986</v>
+        <v>129082719</v>
       </c>
       <c r="B19" t="n">
-        <v>107683</v>
+        <v>106812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219686</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2498,29 +2594,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Skogsberg N om, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521370</v>
+        <v>521498</v>
       </c>
       <c r="R19" t="n">
-        <v>6553485</v>
+        <v>6553177</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,12 +2635,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,50 +2649,46 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Ädellövskog, tidigare ekhage</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133622992</v>
+        <v>129254787</v>
       </c>
       <c r="B20" t="n">
-        <v>107683</v>
+        <v>106812</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219686</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2609,26 +2696,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Testa SO om, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521391</v>
+        <v>521397</v>
       </c>
       <c r="R20" t="n">
-        <v>6553439</v>
+        <v>6553357</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2655,12 +2733,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,7 +2752,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Ädellövskog, tidigare ekhage</t>
+          <t>Lövskog på kalkrik mark</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2685,34 +2763,34 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133622989</v>
+        <v>129260020</v>
       </c>
       <c r="B21" t="n">
-        <v>107683</v>
+        <v>106812</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219686</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2720,29 +2798,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Testa SO om, Nrk</t>
+          <t>Testa, skog SO om, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521397</v>
+        <v>521332</v>
       </c>
       <c r="R21" t="n">
-        <v>6553453</v>
+        <v>6553404</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2766,12 +2835,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,21 +2854,1609 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Ädellövskog, tidigare ekhage</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129260021</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>521411</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6553315</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129260022</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>521374</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6553324</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129259940</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>521340</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6553375</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133622996</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>521367</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6553307</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Björn Gunnarsson</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Björn Gunnarsson</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122905355</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Testaskogen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>521375</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6553266</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129096578</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>521465</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6553182</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129096599</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>521497</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6553139</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129096607</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>521476</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6553172</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129259996</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>521332</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6553404</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129259998</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Testa, skog SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>521340</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6553375</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129096594</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>521437</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6553126</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Lövskog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133622985</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>521357</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6553514</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133622987</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>521347</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6553484</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133622993</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>521361</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6553380</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133622999</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Testa SO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>521427</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6553249</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Ädellövskog, tidigare ekhage</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61646-2023 artfynd.xlsx
+++ b/artfynd/A 61646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096598</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122955281</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1173387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1173388</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096601</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129259884</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096617</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1786,6 +1836,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096573</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1897,6 +1952,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622986</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622988</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2119,6 +2184,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622989</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622990</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2341,6 +2416,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622991</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622992</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2563,6 +2648,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133623000</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2665,6 +2755,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082719</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2767,6 +2862,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254787</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2869,6 +2969,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129260020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2971,6 +3076,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129260021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3073,6 +3183,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129260022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3175,6 +3290,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129259940</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3286,6 +3406,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622996</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3401,6 +3526,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905355</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3503,6 +3633,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096578</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3605,6 +3740,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096599</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3707,6 +3847,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096607</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3809,6 +3954,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129259996</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3911,6 +4061,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129259998</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4013,6 +4168,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096594</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4124,6 +4284,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622985</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4235,6 +4400,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622987</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4346,6 +4516,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622993</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4457,8 +4632,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622999</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>